--- a/Consolidado_Bridge_2025.xlsx
+++ b/Consolidado_Bridge_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08d87aadaabdc2cb/Documentos/nwb/bridge/dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="760" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CD92315-D6B1-4177-AAE6-15662CA249BB}"/>
+  <xr:revisionPtr revIDLastSave="796" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13BAF3EE-1664-4861-A643-05E6D63FF308}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEFB68E0-0739-433A-A945-0FEA615287DD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2025 Consolidado" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025 Consolidado'!$A$1:$P$1375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025 Consolidado'!$C$1:$C$1448</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20684" uniqueCount="3651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21782" uniqueCount="3823">
   <si>
     <t>Quando</t>
   </si>
@@ -11015,6 +11015,522 @@
   </si>
   <si>
     <t>21 97736-9580</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>Paulo Valerio</t>
+  </si>
+  <si>
+    <t>21 97186-8818</t>
+  </si>
+  <si>
+    <t>Max Alexandre Ferreira</t>
+  </si>
+  <si>
+    <t>Sandra Regina</t>
+  </si>
+  <si>
+    <t>Barreiras / BA</t>
+  </si>
+  <si>
+    <t>73 99811-0837</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
+  </si>
+  <si>
+    <t>João Luiz</t>
+  </si>
+  <si>
+    <t>21 99406-1140</t>
+  </si>
+  <si>
+    <t>Daniel Dos Santos Cerqueira</t>
+  </si>
+  <si>
+    <t>21 97021-4572</t>
+  </si>
+  <si>
+    <t>Lucas Juvenal Duarte</t>
+  </si>
+  <si>
+    <t>21 97219-9840</t>
+  </si>
+  <si>
+    <t>Caio Campos</t>
+  </si>
+  <si>
+    <t>21 99495-5189</t>
+  </si>
+  <si>
+    <t>Diego Cabral</t>
+  </si>
+  <si>
+    <t>21 99972-3535</t>
+  </si>
+  <si>
+    <t>Paulo Guillhermo Correira Costa</t>
+  </si>
+  <si>
+    <t>Vila Verdao</t>
+  </si>
+  <si>
+    <t>Jacarepagua  / RJ</t>
+  </si>
+  <si>
+    <t>21 9482-2927</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>ângelo Pereira De Lima</t>
+  </si>
+  <si>
+    <t>21 95922-6452</t>
+  </si>
+  <si>
+    <t>14/12/2025</t>
+  </si>
+  <si>
+    <t>Marcos Antônio Castelo Branco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesquita </t>
+  </si>
+  <si>
+    <t>21 98325-8961</t>
+  </si>
+  <si>
+    <t>Lucas Veiga</t>
+  </si>
+  <si>
+    <t>21 96843-3870</t>
+  </si>
+  <si>
+    <t>Erick Quintanilha</t>
+  </si>
+  <si>
+    <t>21 97106-5337</t>
+  </si>
+  <si>
+    <t>16/12/2025</t>
+  </si>
+  <si>
+    <t>Fábio De Faria Rocha</t>
+  </si>
+  <si>
+    <t>21 98866-1164</t>
+  </si>
+  <si>
+    <t>Renato Torres</t>
+  </si>
+  <si>
+    <t>21 99086-6904</t>
+  </si>
+  <si>
+    <t>21/12/2025</t>
+  </si>
+  <si>
+    <t>Ney Barreiros</t>
+  </si>
+  <si>
+    <t>21 96559-0455</t>
+  </si>
+  <si>
+    <t>Dandara Bernardo Sacramento Dos Santos</t>
+  </si>
+  <si>
+    <t>Del Castilho</t>
+  </si>
+  <si>
+    <t>21 98647-0251</t>
+  </si>
+  <si>
+    <t>Marcos Medeiros</t>
+  </si>
+  <si>
+    <t>21 99383-5758</t>
+  </si>
+  <si>
+    <t>Lucas Amurim</t>
+  </si>
+  <si>
+    <t>21 99077-5922</t>
+  </si>
+  <si>
+    <t>28/12/2025</t>
+  </si>
+  <si>
+    <t>Gilvan Junior</t>
+  </si>
+  <si>
+    <t>21 98089-8752</t>
+  </si>
+  <si>
+    <t>José Geraldo De Menezes</t>
+  </si>
+  <si>
+    <t>21 99061-7085</t>
+  </si>
+  <si>
+    <t>Paulo Melo</t>
+  </si>
+  <si>
+    <t>21 98216-3821</t>
+  </si>
+  <si>
+    <t>Carlos Pereir</t>
+  </si>
+  <si>
+    <t>21 99691-0114</t>
+  </si>
+  <si>
+    <t>Thiago Cerqueira</t>
+  </si>
+  <si>
+    <t>Real Parque</t>
+  </si>
+  <si>
+    <t>11 96092-9648</t>
+  </si>
+  <si>
+    <t>Paulo Cesar</t>
+  </si>
+  <si>
+    <t>21 96943-2782</t>
+  </si>
+  <si>
+    <t>Pedro Freitas</t>
+  </si>
+  <si>
+    <t>21 99884-7902</t>
+  </si>
+  <si>
+    <t>Pablo Rezende Rodrigues</t>
+  </si>
+  <si>
+    <t>Fanchem</t>
+  </si>
+  <si>
+    <t>Queimados / RJ</t>
+  </si>
+  <si>
+    <t>21 98688-1253</t>
+  </si>
+  <si>
+    <t>Marina Fernandes</t>
+  </si>
+  <si>
+    <t>21 99687-8583</t>
+  </si>
+  <si>
+    <t>Laura Araújo</t>
+  </si>
+  <si>
+    <t>21 96599-8745</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>Carla Oliveira</t>
+  </si>
+  <si>
+    <t>21 97657-6486</t>
+  </si>
+  <si>
+    <t>Ingrid Abreu Freitas</t>
+  </si>
+  <si>
+    <t>21 99820-2061</t>
+  </si>
+  <si>
+    <t>Joyce De Almeida Sameirl</t>
+  </si>
+  <si>
+    <t>21 97110-5113</t>
+  </si>
+  <si>
+    <t>Giovanna Maciel</t>
+  </si>
+  <si>
+    <t>21 99114-8239</t>
+  </si>
+  <si>
+    <t>Cirley Carvalho Oliveira</t>
+  </si>
+  <si>
+    <t>11 94006-0232</t>
+  </si>
+  <si>
+    <t>Paula Monique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abolição </t>
+  </si>
+  <si>
+    <t>21 97649-5776</t>
+  </si>
+  <si>
+    <t>Patrícia Bernardo De Souza</t>
+  </si>
+  <si>
+    <t>21 97025-6232</t>
+  </si>
+  <si>
+    <t>Nithelly Souza</t>
+  </si>
+  <si>
+    <t>21 99614-6273</t>
+  </si>
+  <si>
+    <t>Elisangela Maria Cardoso</t>
+  </si>
+  <si>
+    <t>21 99876-1856</t>
+  </si>
+  <si>
+    <t>Nathalya Felipe Cardoso</t>
+  </si>
+  <si>
+    <t>21 97495-0656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monica </t>
+  </si>
+  <si>
+    <t>21 99955-8335</t>
+  </si>
+  <si>
+    <t>Larissa Ximenes</t>
+  </si>
+  <si>
+    <t>21 97002-6229</t>
+  </si>
+  <si>
+    <t>Andréia Lopes</t>
+  </si>
+  <si>
+    <t>Nova Cidade</t>
+  </si>
+  <si>
+    <t>21 99973-4482</t>
+  </si>
+  <si>
+    <t>Renata Santana</t>
+  </si>
+  <si>
+    <t>21 98208-3945</t>
+  </si>
+  <si>
+    <t>Luzia Cardoso Dos Santos</t>
+  </si>
+  <si>
+    <t>24 99915-1832</t>
+  </si>
+  <si>
+    <t>Valdine De Jesus Bispo</t>
+  </si>
+  <si>
+    <t>21 96483-5332</t>
+  </si>
+  <si>
+    <t>Francilene Mesquita E Souza</t>
+  </si>
+  <si>
+    <t>Estrada Da Gávea 486</t>
+  </si>
+  <si>
+    <t>Fernanda Santos Silva</t>
+  </si>
+  <si>
+    <t>21 96410-4033</t>
+  </si>
+  <si>
+    <t>Thamara Menezes</t>
+  </si>
+  <si>
+    <t>21 97105-1777</t>
+  </si>
+  <si>
+    <t>Chrislane Kellen</t>
+  </si>
+  <si>
+    <t>31 7174-2285</t>
+  </si>
+  <si>
+    <t>Júlia Hanzel Masutti</t>
+  </si>
+  <si>
+    <t>21 99991-1735</t>
+  </si>
+  <si>
+    <t>Isadora Costa</t>
+  </si>
+  <si>
+    <t>21 98312-3627</t>
+  </si>
+  <si>
+    <t>Ana Maria Siqueira De Souza</t>
+  </si>
+  <si>
+    <t>21 98377-6387</t>
+  </si>
+  <si>
+    <t>Marines Souza</t>
+  </si>
+  <si>
+    <t>Porto Alegre / --</t>
+  </si>
+  <si>
+    <t>51 99398-8243</t>
+  </si>
+  <si>
+    <t>Carla Dias</t>
+  </si>
+  <si>
+    <t>21 98659-9696</t>
+  </si>
+  <si>
+    <t>Tereza Silva</t>
+  </si>
+  <si>
+    <t>Botofogo</t>
+  </si>
+  <si>
+    <t>21 99935-4616</t>
+  </si>
+  <si>
+    <t>Daniele Monteiro Pesanha Eboli</t>
+  </si>
+  <si>
+    <t>21 97723-8541</t>
+  </si>
+  <si>
+    <t>Simone Oliveira</t>
+  </si>
+  <si>
+    <t>21 97091-7232</t>
+  </si>
+  <si>
+    <t>Raquel Rodrigues</t>
+  </si>
+  <si>
+    <t>21 96909-0473</t>
+  </si>
+  <si>
+    <t>Carolina Castelo Branco</t>
+  </si>
+  <si>
+    <t>21 96876-7966</t>
+  </si>
+  <si>
+    <t>Tania Alves</t>
+  </si>
+  <si>
+    <t>21 98404-1652</t>
+  </si>
+  <si>
+    <t>Vanessa Lorraine</t>
+  </si>
+  <si>
+    <t>21 98542-1249</t>
+  </si>
+  <si>
+    <t>Natália Evelyn</t>
+  </si>
+  <si>
+    <t>11 92095-9854</t>
+  </si>
+  <si>
+    <t>Joana Navarro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardim Caravelas </t>
+  </si>
+  <si>
+    <t>São Paulo  / --</t>
+  </si>
+  <si>
+    <t>21 98228-4356</t>
+  </si>
+  <si>
+    <t>Ana Patricia Lemos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duque De Caxias </t>
+  </si>
+  <si>
+    <t>21 99958-1032</t>
+  </si>
+  <si>
+    <t>Luiza Lemos Castello Branco Ribeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 De Agosto </t>
+  </si>
+  <si>
+    <t>21 99820-7006</t>
+  </si>
+  <si>
+    <t>Karol Lima</t>
+  </si>
+  <si>
+    <t>21 97611-4078</t>
+  </si>
+  <si>
+    <t>Laura Cliliano</t>
+  </si>
+  <si>
+    <t>21 97663-9105</t>
+  </si>
+  <si>
+    <t>Rachel Mandarine</t>
+  </si>
+  <si>
+    <t>21 97943-3694</t>
+  </si>
+  <si>
+    <t>Ivanilde Rodrigues Gomes</t>
+  </si>
+  <si>
+    <t>21 98586-0663</t>
+  </si>
+  <si>
+    <t>Mirtes Mota De Menezes</t>
+  </si>
+  <si>
+    <t>21 99372-9361</t>
+  </si>
+  <si>
+    <t>Mariana Assunção</t>
+  </si>
+  <si>
+    <t>21 98232-3798</t>
+  </si>
+  <si>
+    <t>Nicole Volkov</t>
+  </si>
+  <si>
+    <t>21 99991-2602</t>
+  </si>
+  <si>
+    <t>Larissa Thereza Do Carmo</t>
+  </si>
+  <si>
+    <t>Butantã</t>
+  </si>
+  <si>
+    <t>11 97512-4606</t>
+  </si>
+  <si>
+    <t>Monique Gomez</t>
+  </si>
+  <si>
+    <t>21 97411-0770</t>
   </si>
 </sst>
 </file>
@@ -11070,7 +11586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11081,6 +11597,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11419,7 +11941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F662FB8-528C-4013-B4C5-67C7C16EE720}">
-  <dimension ref="A1:P1375"/>
+  <dimension ref="A1:P1448"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -24116,8 +24638,11 @@
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
+      <c r="A255" s="6" t="s">
         <v>780</v>
+      </c>
+      <c r="C255" t="s">
+        <v>41</v>
       </c>
       <c r="D255" t="s">
         <v>887</v>
@@ -24146,8 +24671,11 @@
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
+      <c r="A256" s="6" t="s">
         <v>780</v>
+      </c>
+      <c r="C256" t="s">
+        <v>41</v>
       </c>
       <c r="D256" t="s">
         <v>891</v>
@@ -26116,8 +26644,11 @@
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A296" s="5">
+      <c r="A296" s="7">
         <v>45739</v>
+      </c>
+      <c r="C296" t="s">
+        <v>41</v>
       </c>
       <c r="D296" t="s">
         <v>1011</v>
@@ -80092,7 +80623,3658 @@
         <v>823</v>
       </c>
     </row>
+    <row r="1376" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1376" t="s">
+        <v>3651</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>3652</v>
+      </c>
+      <c r="E1376" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1376" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1376">
+        <v>39</v>
+      </c>
+      <c r="H1376" t="s">
+        <v>1712</v>
+      </c>
+      <c r="I1376" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1376" t="s">
+        <v>3653</v>
+      </c>
+      <c r="K1376" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1376" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1376" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1376" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1376" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1376" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1377" t="s">
+        <v>3651</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>3654</v>
+      </c>
+      <c r="E1377" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1377" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1377">
+        <v>43</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>3655</v>
+      </c>
+      <c r="I1377" t="s">
+        <v>3656</v>
+      </c>
+      <c r="J1377" t="s">
+        <v>3657</v>
+      </c>
+      <c r="K1377" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1377" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1377" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1377" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1377" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1377" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1378" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>3659</v>
+      </c>
+      <c r="E1378" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1378" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1378">
+        <v>47</v>
+      </c>
+      <c r="H1378" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I1378" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1378" t="s">
+        <v>3660</v>
+      </c>
+      <c r="K1378" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1378" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1378" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1378" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1378" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1378" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1379" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>3661</v>
+      </c>
+      <c r="E1379" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1379" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1379">
+        <v>24</v>
+      </c>
+      <c r="H1379" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1379" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1379" t="s">
+        <v>3662</v>
+      </c>
+      <c r="K1379" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1379" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1379" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1379" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1379" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1379" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1380" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>3663</v>
+      </c>
+      <c r="E1380" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1380" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1380">
+        <v>21</v>
+      </c>
+      <c r="H1380" t="s">
+        <v>1992</v>
+      </c>
+      <c r="I1380" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1380" t="s">
+        <v>3664</v>
+      </c>
+      <c r="K1380" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1380" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1380" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1380" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1380" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1380" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1381" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>3665</v>
+      </c>
+      <c r="E1381" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1381" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1381">
+        <v>30</v>
+      </c>
+      <c r="H1381" t="s">
+        <v>511</v>
+      </c>
+      <c r="I1381" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1381" t="s">
+        <v>3666</v>
+      </c>
+      <c r="K1381" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1381" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1381" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1381" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1381" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1381" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1382" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>3667</v>
+      </c>
+      <c r="E1382" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1382" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1382">
+        <v>30</v>
+      </c>
+      <c r="H1382" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1382" t="s">
+        <v>3668</v>
+      </c>
+      <c r="K1382" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1382" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1382" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1382" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1382" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1382" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1383" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>3669</v>
+      </c>
+      <c r="E1383" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1383" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1383">
+        <v>30</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>3670</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>3671</v>
+      </c>
+      <c r="J1383" t="s">
+        <v>3672</v>
+      </c>
+      <c r="K1383" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1383" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1383" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1383" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1383" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1383" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1384" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>3674</v>
+      </c>
+      <c r="E1384" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1384" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1384">
+        <v>38</v>
+      </c>
+      <c r="H1384" t="s">
+        <v>1422</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1384" t="s">
+        <v>3675</v>
+      </c>
+      <c r="K1384" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1384" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1384" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1384" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1384" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1384" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1385" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>3677</v>
+      </c>
+      <c r="E1385" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1385">
+        <v>30</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>3678</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1385" t="s">
+        <v>3679</v>
+      </c>
+      <c r="K1385" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1385" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1385" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1385" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1385" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1385" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1386" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>3680</v>
+      </c>
+      <c r="E1386" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1386" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1386">
+        <v>28</v>
+      </c>
+      <c r="H1386" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1386" t="s">
+        <v>3681</v>
+      </c>
+      <c r="K1386" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1386" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1386" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1386" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1386" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1386" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1387" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>3682</v>
+      </c>
+      <c r="E1387" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1387" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1387">
+        <v>30</v>
+      </c>
+      <c r="H1387" t="s">
+        <v>365</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1387" t="s">
+        <v>3683</v>
+      </c>
+      <c r="K1387" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1387" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1387" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1387" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1387" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1387" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1388" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>3685</v>
+      </c>
+      <c r="E1388" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1388">
+        <v>46</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>501</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1388" t="s">
+        <v>3686</v>
+      </c>
+      <c r="K1388" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1388" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1388" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1388" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1388" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1388" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1389" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>3687</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1389">
+        <v>53</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1389" t="s">
+        <v>3688</v>
+      </c>
+      <c r="K1389" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1389" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1389" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1389" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1389" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1389" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1390" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>3690</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1390">
+        <v>37</v>
+      </c>
+      <c r="H1390" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1390" t="s">
+        <v>3691</v>
+      </c>
+      <c r="K1390" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1390" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1390" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1390" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1390" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1390" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1391" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>3692</v>
+      </c>
+      <c r="E1391" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1391" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1391">
+        <v>43</v>
+      </c>
+      <c r="H1391" t="s">
+        <v>3693</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1391" t="s">
+        <v>3694</v>
+      </c>
+      <c r="K1391" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1391" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1391" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1391" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1391" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1391" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1392" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>3695</v>
+      </c>
+      <c r="E1392" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1392" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1392">
+        <v>36</v>
+      </c>
+      <c r="H1392" t="s">
+        <v>365</v>
+      </c>
+      <c r="I1392" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1392" t="s">
+        <v>3696</v>
+      </c>
+      <c r="K1392" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1392" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1392" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1392" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1392" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1392" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1393" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>3697</v>
+      </c>
+      <c r="E1393" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1393" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1393">
+        <v>23</v>
+      </c>
+      <c r="H1393" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I1393" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1393" t="s">
+        <v>3698</v>
+      </c>
+      <c r="K1393" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1393" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1393" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1393" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1393" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1393" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1394" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>3700</v>
+      </c>
+      <c r="E1394" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1394" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1394">
+        <v>34</v>
+      </c>
+      <c r="H1394" t="s">
+        <v>617</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1394" t="s">
+        <v>3701</v>
+      </c>
+      <c r="K1394" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1394" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1394" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1394" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1394" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1394" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1395" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>3702</v>
+      </c>
+      <c r="E1395" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1395">
+        <v>77</v>
+      </c>
+      <c r="H1395" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1395" t="s">
+        <v>3703</v>
+      </c>
+      <c r="K1395" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1395" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1395" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1395" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1395" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1395" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1396" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>3704</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1396" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1396">
+        <v>30</v>
+      </c>
+      <c r="H1396" t="s">
+        <v>617</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1396" t="s">
+        <v>3705</v>
+      </c>
+      <c r="K1396" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1396" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1396" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1396" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1396" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1396" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1397" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>3706</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1397">
+        <v>30</v>
+      </c>
+      <c r="H1397" t="s">
+        <v>617</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1397" t="s">
+        <v>3707</v>
+      </c>
+      <c r="K1397" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1397" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1397" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1397" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1397" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1397" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1398" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>3708</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1398">
+        <v>38</v>
+      </c>
+      <c r="H1398" t="s">
+        <v>3709</v>
+      </c>
+      <c r="I1398" t="s">
+        <v>540</v>
+      </c>
+      <c r="J1398" t="s">
+        <v>3710</v>
+      </c>
+      <c r="K1398" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1398" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1398" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1398" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1398" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1398" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1399" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>3711</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1399">
+        <v>22</v>
+      </c>
+      <c r="H1399" t="s">
+        <v>365</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1399" t="s">
+        <v>3712</v>
+      </c>
+      <c r="K1399" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1399" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1399" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1399" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1399" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1399" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1400" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>3713</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1400" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1400">
+        <v>29</v>
+      </c>
+      <c r="H1400" t="s">
+        <v>617</v>
+      </c>
+      <c r="I1400" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1400" t="s">
+        <v>3714</v>
+      </c>
+      <c r="K1400" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1400" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1400" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1400" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1400" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1400" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1401" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>3715</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1401" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1401">
+        <v>30</v>
+      </c>
+      <c r="H1401" t="s">
+        <v>3716</v>
+      </c>
+      <c r="I1401" t="s">
+        <v>3717</v>
+      </c>
+      <c r="J1401" t="s">
+        <v>3718</v>
+      </c>
+      <c r="K1401" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1401" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1401" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1401" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1401" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1401" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1402" t="s">
+        <v>3651</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>3719</v>
+      </c>
+      <c r="E1402" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1402">
+        <v>39</v>
+      </c>
+      <c r="H1402" t="s">
+        <v>2000</v>
+      </c>
+      <c r="I1402" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1402" t="s">
+        <v>3720</v>
+      </c>
+      <c r="K1402" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1402" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1402" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1402" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1402" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1402" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1403" t="s">
+        <v>3651</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>3721</v>
+      </c>
+      <c r="E1403" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1403" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1403">
+        <v>19</v>
+      </c>
+      <c r="H1403" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1403" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1403" t="s">
+        <v>3722</v>
+      </c>
+      <c r="K1403" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1403" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1403" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1403" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1403" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1403" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1404" t="s">
+        <v>3723</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>3724</v>
+      </c>
+      <c r="E1404" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1404" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1404">
+        <v>30</v>
+      </c>
+      <c r="H1404" t="s">
+        <v>365</v>
+      </c>
+      <c r="I1404" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1404" t="s">
+        <v>3725</v>
+      </c>
+      <c r="K1404" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1404" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1404" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1404" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1404" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1404" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1405" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>3726</v>
+      </c>
+      <c r="E1405" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1405" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1405">
+        <v>30</v>
+      </c>
+      <c r="H1405" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1405" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1405" t="s">
+        <v>3727</v>
+      </c>
+      <c r="K1405" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1405" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1405" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1405" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1405" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1405" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1406" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>3728</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1406">
+        <v>39</v>
+      </c>
+      <c r="H1406" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1406" t="s">
+        <v>3729</v>
+      </c>
+      <c r="K1406" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1406" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1406" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1406" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1406" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1406" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1407" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>3730</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1407">
+        <v>18</v>
+      </c>
+      <c r="H1407" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1407" t="s">
+        <v>3731</v>
+      </c>
+      <c r="K1407" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1407" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1407" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1407" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1407" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1407" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1408" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>3732</v>
+      </c>
+      <c r="E1408" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1408">
+        <v>38</v>
+      </c>
+      <c r="H1408" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>1159</v>
+      </c>
+      <c r="J1408" t="s">
+        <v>3733</v>
+      </c>
+      <c r="K1408" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1408" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1408" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1408" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1408" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1408" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1409" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>3734</v>
+      </c>
+      <c r="E1409" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1409">
+        <v>30</v>
+      </c>
+      <c r="H1409" t="s">
+        <v>3735</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1409" t="s">
+        <v>3736</v>
+      </c>
+      <c r="K1409" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1409" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1409" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1409" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1409" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1409" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1410" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>3737</v>
+      </c>
+      <c r="E1410" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1410">
+        <v>45</v>
+      </c>
+      <c r="H1410" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1410" t="s">
+        <v>3738</v>
+      </c>
+      <c r="K1410" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1410" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1410" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1410" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1410" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1410" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1411" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>3739</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1411">
+        <v>22</v>
+      </c>
+      <c r="H1411" t="s">
+        <v>2639</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1411" t="s">
+        <v>3740</v>
+      </c>
+      <c r="K1411" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1411" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1411" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1411" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1411" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1411" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1412" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>3741</v>
+      </c>
+      <c r="E1412" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1412" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1412">
+        <v>46</v>
+      </c>
+      <c r="H1412" t="s">
+        <v>545</v>
+      </c>
+      <c r="I1412" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1412" t="s">
+        <v>3742</v>
+      </c>
+      <c r="K1412" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1412" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1412" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1412" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1412" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1412" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1413" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>3743</v>
+      </c>
+      <c r="E1413" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>184</v>
+      </c>
+      <c r="G1413">
+        <v>35</v>
+      </c>
+      <c r="H1413" t="s">
+        <v>2802</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1413" t="s">
+        <v>3744</v>
+      </c>
+      <c r="K1413" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1413" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1413" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1413" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1413" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1413" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1414" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>3745</v>
+      </c>
+      <c r="E1414" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1414">
+        <v>30</v>
+      </c>
+      <c r="H1414" t="s">
+        <v>2561</v>
+      </c>
+      <c r="I1414" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1414" t="s">
+        <v>3746</v>
+      </c>
+      <c r="K1414" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1414" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1414" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1414" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1414" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1414" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1415" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>3747</v>
+      </c>
+      <c r="E1415" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1415">
+        <v>25</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1415" t="s">
+        <v>3748</v>
+      </c>
+      <c r="K1415" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1415" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1415" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1415" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1415" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1415" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1416" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>3749</v>
+      </c>
+      <c r="E1416" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1416" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1416">
+        <v>58</v>
+      </c>
+      <c r="H1416" t="s">
+        <v>3750</v>
+      </c>
+      <c r="I1416" t="s">
+        <v>645</v>
+      </c>
+      <c r="J1416" t="s">
+        <v>3751</v>
+      </c>
+      <c r="K1416" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1416" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1416" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1416" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1416" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1416" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1417" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>3752</v>
+      </c>
+      <c r="E1417" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1417">
+        <v>53</v>
+      </c>
+      <c r="H1417" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1417" t="s">
+        <v>3753</v>
+      </c>
+      <c r="K1417" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1417" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1417" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1417" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1417" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1417" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1418" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>3754</v>
+      </c>
+      <c r="E1418" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1418" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1418">
+        <v>78</v>
+      </c>
+      <c r="H1418" t="s">
+        <v>2000</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1418" t="s">
+        <v>3755</v>
+      </c>
+      <c r="K1418" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1418" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1418" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1418" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1418" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1418" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1419" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>3756</v>
+      </c>
+      <c r="E1419" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1419" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1419">
+        <v>58</v>
+      </c>
+      <c r="H1419" t="s">
+        <v>326</v>
+      </c>
+      <c r="I1419" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1419" t="s">
+        <v>3757</v>
+      </c>
+      <c r="K1419" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1419" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1419" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1419" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1419" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1419" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1420" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>3758</v>
+      </c>
+      <c r="E1420" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1420" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1420">
+        <v>47</v>
+      </c>
+      <c r="H1420" t="s">
+        <v>3759</v>
+      </c>
+      <c r="I1420" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1420" t="s">
+        <v>975</v>
+      </c>
+      <c r="K1420" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1420" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1420" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1420" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1420" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1420" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1421" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>3760</v>
+      </c>
+      <c r="E1421" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1421" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1421">
+        <v>43</v>
+      </c>
+      <c r="H1421" t="s">
+        <v>2000</v>
+      </c>
+      <c r="I1421" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1421" t="s">
+        <v>3761</v>
+      </c>
+      <c r="K1421" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1421" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1421" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1421" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1421" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1421" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1422" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>3762</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1422">
+        <v>38</v>
+      </c>
+      <c r="H1422" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1422" t="s">
+        <v>3763</v>
+      </c>
+      <c r="K1422" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1422" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1422" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1422" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1422" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1422" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1423" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>3764</v>
+      </c>
+      <c r="E1423" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1423" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1423">
+        <v>37</v>
+      </c>
+      <c r="H1423" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1423" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1423" t="s">
+        <v>3765</v>
+      </c>
+      <c r="K1423" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1423" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1423" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1423" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1423" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1423" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1424" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>3766</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1424">
+        <v>27</v>
+      </c>
+      <c r="H1424" t="s">
+        <v>2526</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1424" t="s">
+        <v>3767</v>
+      </c>
+      <c r="K1424" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1424" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1424" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1424" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1424" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1424" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1425" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>3768</v>
+      </c>
+      <c r="E1425" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1425" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1425">
+        <v>19</v>
+      </c>
+      <c r="H1425" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I1425" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1425" t="s">
+        <v>3769</v>
+      </c>
+      <c r="K1425" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1425" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1425" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1425" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1425" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1425" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1426" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>3770</v>
+      </c>
+      <c r="E1426" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1426">
+        <v>36</v>
+      </c>
+      <c r="H1426" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1426" t="s">
+        <v>3771</v>
+      </c>
+      <c r="K1426" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1426" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1426" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1426" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1426" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1426" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1427" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>3772</v>
+      </c>
+      <c r="E1427" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1427" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1427">
+        <v>65</v>
+      </c>
+      <c r="H1427" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1427" t="s">
+        <v>3773</v>
+      </c>
+      <c r="J1427" t="s">
+        <v>3774</v>
+      </c>
+      <c r="K1427" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1427" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1427" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1427" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1427" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1427" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1428" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>3775</v>
+      </c>
+      <c r="E1428" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1428" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1428">
+        <v>49</v>
+      </c>
+      <c r="H1428" t="s">
+        <v>908</v>
+      </c>
+      <c r="I1428" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1428" t="s">
+        <v>3776</v>
+      </c>
+      <c r="K1428" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1428" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1428" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1428" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1428" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1428" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1429" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>3777</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1429">
+        <v>56</v>
+      </c>
+      <c r="H1429" t="s">
+        <v>3778</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1429" t="s">
+        <v>3779</v>
+      </c>
+      <c r="K1429" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1429" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1429" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1429" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1429" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1429" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1430" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>3780</v>
+      </c>
+      <c r="E1430" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1430" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1430">
+        <v>46</v>
+      </c>
+      <c r="H1430" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1430" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1430" t="s">
+        <v>3781</v>
+      </c>
+      <c r="K1430" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1430" t="s">
+        <v>449</v>
+      </c>
+      <c r="M1430" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1430" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1430" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1430" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1431" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>3782</v>
+      </c>
+      <c r="E1431" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1431" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1431">
+        <v>38</v>
+      </c>
+      <c r="H1431" t="s">
+        <v>501</v>
+      </c>
+      <c r="I1431" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1431" t="s">
+        <v>3783</v>
+      </c>
+      <c r="K1431" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1431" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1431" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1431" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1431" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1431" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1432" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>3784</v>
+      </c>
+      <c r="E1432" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1432">
+        <v>30</v>
+      </c>
+      <c r="H1432" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1432" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1432" t="s">
+        <v>3785</v>
+      </c>
+      <c r="K1432" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1432" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1432" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1432" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1432" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1432" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1433" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>3786</v>
+      </c>
+      <c r="E1433" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1433">
+        <v>31</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>3499</v>
+      </c>
+      <c r="I1433" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1433" t="s">
+        <v>3787</v>
+      </c>
+      <c r="K1433" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1433" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1433" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1433" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1433" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1433" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1434" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>3788</v>
+      </c>
+      <c r="E1434" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1434" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1434">
+        <v>33</v>
+      </c>
+      <c r="H1434" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1434" t="s">
+        <v>3789</v>
+      </c>
+      <c r="K1434" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1434" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1434" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1434" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1434" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1434" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1435" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>3790</v>
+      </c>
+      <c r="E1435" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1435" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1435">
+        <v>30</v>
+      </c>
+      <c r="H1435" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1435" t="s">
+        <v>3791</v>
+      </c>
+      <c r="K1435" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1435" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1435" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1435" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1435" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1435" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1436" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>3792</v>
+      </c>
+      <c r="E1436" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1436" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1436">
+        <v>26</v>
+      </c>
+      <c r="H1436" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I1436" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1436" t="s">
+        <v>3793</v>
+      </c>
+      <c r="K1436" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1436" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1436" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1436" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1436" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1436" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1437" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>3794</v>
+      </c>
+      <c r="E1437" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1437" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1437">
+        <v>40</v>
+      </c>
+      <c r="H1437" t="s">
+        <v>3795</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>3796</v>
+      </c>
+      <c r="J1437" t="s">
+        <v>3797</v>
+      </c>
+      <c r="K1437" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1437" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1437" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1437" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1437" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1437" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1438" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>3798</v>
+      </c>
+      <c r="E1438" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1438">
+        <v>49</v>
+      </c>
+      <c r="H1438" t="s">
+        <v>3799</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>688</v>
+      </c>
+      <c r="J1438" t="s">
+        <v>3800</v>
+      </c>
+      <c r="K1438" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1438" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1438" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1438" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1438" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1438" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1439" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>3801</v>
+      </c>
+      <c r="E1439" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1439" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1439">
+        <v>20</v>
+      </c>
+      <c r="H1439" t="s">
+        <v>3802</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>688</v>
+      </c>
+      <c r="J1439" t="s">
+        <v>3803</v>
+      </c>
+      <c r="K1439" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1439" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1439" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1439" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1439" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1439" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1440" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>3804</v>
+      </c>
+      <c r="E1440" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1440" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1440">
+        <v>31</v>
+      </c>
+      <c r="H1440" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1440" t="s">
+        <v>3805</v>
+      </c>
+      <c r="K1440" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1440" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1440" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1440" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1440" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1440" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1441" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>3806</v>
+      </c>
+      <c r="E1441" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1441" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1441">
+        <v>16</v>
+      </c>
+      <c r="H1441" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I1441" t="s">
+        <v>334</v>
+      </c>
+      <c r="J1441" t="s">
+        <v>3807</v>
+      </c>
+      <c r="K1441" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1441" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1441" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1441" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1441" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1441" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1442" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>3808</v>
+      </c>
+      <c r="E1442" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1442" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1442">
+        <v>42</v>
+      </c>
+      <c r="H1442" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1442" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1442" t="s">
+        <v>3809</v>
+      </c>
+      <c r="K1442" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1442" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1442" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1442" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1442" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1442" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1443" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>3810</v>
+      </c>
+      <c r="E1443" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1443">
+        <v>54</v>
+      </c>
+      <c r="H1443" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I1443" t="s">
+        <v>1159</v>
+      </c>
+      <c r="J1443" t="s">
+        <v>3811</v>
+      </c>
+      <c r="K1443" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1443" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1443" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1443" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1443" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1443" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1444" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>3812</v>
+      </c>
+      <c r="E1444" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1444">
+        <v>72</v>
+      </c>
+      <c r="H1444" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I1444" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1444" t="s">
+        <v>3813</v>
+      </c>
+      <c r="K1444" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1444" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1444" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1444" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1444" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1444" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1445" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>3814</v>
+      </c>
+      <c r="E1445" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1445">
+        <v>32</v>
+      </c>
+      <c r="H1445" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1445" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1445" t="s">
+        <v>3815</v>
+      </c>
+      <c r="K1445" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1445" t="s">
+        <v>456</v>
+      </c>
+      <c r="M1445" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1445" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1445" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1445" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1446" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>3816</v>
+      </c>
+      <c r="E1446" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1446">
+        <v>14</v>
+      </c>
+      <c r="H1446" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1446" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1446" t="s">
+        <v>3817</v>
+      </c>
+      <c r="K1446" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1446" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1446" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1446" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1446" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1446" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1447" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>3818</v>
+      </c>
+      <c r="E1447" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1447">
+        <v>31</v>
+      </c>
+      <c r="H1447" t="s">
+        <v>3819</v>
+      </c>
+      <c r="I1447" t="s">
+        <v>540</v>
+      </c>
+      <c r="J1447" t="s">
+        <v>3820</v>
+      </c>
+      <c r="K1447" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1447" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1447" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1447" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1447" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1447" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1448" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>3821</v>
+      </c>
+      <c r="E1448" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1448">
+        <v>34</v>
+      </c>
+      <c r="H1448" t="s">
+        <v>2940</v>
+      </c>
+      <c r="I1448" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1448" t="s">
+        <v>3822</v>
+      </c>
+      <c r="K1448" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1448" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1448" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1448" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1448" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1448" t="s">
+        <v>823</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="C1:C1448" xr:uid="{2F662FB8-528C-4013-B4C5-67C7C16EE720}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>